--- a/plantilla_presupuesto.xlsx
+++ b/plantilla_presupuesto.xlsx
@@ -500,7 +500,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -516,7 +516,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Cliente</v>
+        <v>Código cliente (vacío o 1000 = sin código)</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -524,7 +524,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Contacto</v>
+        <v>Cliente</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -532,7 +532,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Referencia</v>
+        <v>Contacto</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -540,7 +540,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Descripción</v>
+        <v>Referencia</v>
       </c>
       <c r="B5" t="str">
         <v/>
@@ -548,15 +548,23 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>Descripción</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>Descuento carpintero (Sí / No)</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B7" t="str">
         <v>No</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/plantilla_presupuesto.xlsx
+++ b/plantilla_presupuesto.xlsx
@@ -6,8 +6,9 @@
     <sheet name="Instrucciones" sheetId="1" r:id="rId1"/>
     <sheet name="Datos" sheetId="2" r:id="rId2"/>
     <sheet name="Piezas" sheetId="3" r:id="rId3"/>
-    <sheet name="Extras" sheetId="4" r:id="rId4"/>
-    <sheet name="Materiales" sheetId="5" r:id="rId5"/>
+    <sheet name="Herrajes" sheetId="4" r:id="rId4"/>
+    <sheet name="Extras" sheetId="5" r:id="rId5"/>
+    <sheet name="Materiales" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -428,7 +429,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>3. En «Extras» pon los herrajes y accesorios de cada mueble.</v>
+        <v>3. En «Herrajes» pon las bisagras, cajones… de cada mueble, y en «Extras» el resto de accesorios.</v>
       </c>
     </row>
     <row r="6">
@@ -458,7 +459,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>• Cantos: L1 L2 A1 A2 (separados por espacios), «todos», «largos» o «anchos». Vacío = sin canto.</v>
+        <v>• Cantos: L1 L2 A1 A2 (separados por espacios), «todos», «largos» o «anchos». Vacío = sin canto. En materiales pulidos (MDF) son los lados que se pulen.</v>
       </c>
     </row>
     <row r="12">
@@ -483,7 +484,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>En «Extras», si dejas el precio vacío se usa el del catálogo.</v>
+        <v>En «Herrajes» y «Extras», si dejas el precio vacío se usa el del catálogo.</v>
       </c>
     </row>
     <row r="17">
@@ -500,7 +501,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <cols>
     <col min="1" max="1" width="32.83203125" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -516,7 +517,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Cliente</v>
+        <v>Código cliente (vacío o 1000 = sin código)</v>
       </c>
       <c r="B2" t="str">
         <v/>
@@ -524,7 +525,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Contacto</v>
+        <v>Cliente</v>
       </c>
       <c r="B3" t="str">
         <v/>
@@ -532,7 +533,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Referencia</v>
+        <v>Contacto</v>
       </c>
       <c r="B4" t="str">
         <v/>
@@ -540,7 +541,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Descripción</v>
+        <v>Referencia</v>
       </c>
       <c r="B5" t="str">
         <v/>
@@ -548,15 +549,23 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>Descripción</v>
+      </c>
+      <c r="B6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>Descuento carpintero (Sí / No)</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B7" t="str">
         <v>No</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -740,7 +749,7 @@
         <v>Mueble</v>
       </c>
       <c r="B1" t="str">
-        <v>Producto</v>
+        <v>Herraje</v>
       </c>
       <c r="C1" t="str">
         <v>Precio (€/ud)</v>
@@ -772,7 +781,52 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:D2"/>
+  <cols>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Mueble</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Producto</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Precio (€/ud)</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Cantidad</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Armario dormitorio</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Escambell Calaixos</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G44"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="34.83203125" customWidth="1"/>
@@ -1475,9 +1529,12 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Extras del catálogo</v>
+        <v>Herrajes del catálogo</v>
       </c>
       <c r="B32" t="str">
+        <v>Tipo</v>
+      </c>
+      <c r="C32" t="str">
         <v>Precio (€/ud)</v>
       </c>
     </row>
@@ -1485,85 +1542,111 @@
       <c r="A33" t="str">
         <v>Bissagra Amortiguada</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="str">
+        <v>Bisagras</v>
+      </c>
+      <c r="C33">
         <v>2.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Nivellador base</v>
-      </c>
-      <c r="B34">
-        <v>1.45</v>
+        <v>Calaix guia Emuca</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Cajones</v>
+      </c>
+      <c r="C34">
+        <v>52.51</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Barra Penjador</v>
-      </c>
-      <c r="B35">
-        <v>2.75</v>
+        <v>Calaix guia Blum</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Cajones</v>
+      </c>
+      <c r="C35">
+        <v>81.94</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Suport barra</v>
-      </c>
-      <c r="B36">
-        <v>0.27</v>
+        <v>Barra Penjador</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Colgadores</v>
+      </c>
+      <c r="C36">
+        <v>2.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Calaix guia Emuca</v>
-      </c>
-      <c r="B37">
-        <v>52.51</v>
+        <v>Suport barra</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Colgadores</v>
+      </c>
+      <c r="C37">
+        <v>0.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Calaix guia Blum</v>
-      </c>
-      <c r="B38">
-        <v>81.94</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Escambell Calaixos</v>
-      </c>
-      <c r="B39">
-        <v>50</v>
+        <v>Nivellador base</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Niveladores</v>
+      </c>
+      <c r="C38">
+        <v>1.45</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Fressat Unyero</v>
-      </c>
-      <c r="B40">
-        <v>11.66</v>
+        <v>Extras del catálogo</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Precio (€/ud)</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Fressat LED</v>
+        <v>Escambell Calaixos</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
+        <v>Fressat Unyero</v>
+      </c>
+      <c r="B42">
+        <v>11.66</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Fressat LED</v>
+      </c>
+      <c r="B43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
         <v>Base Armari</v>
       </c>
-      <c r="B42">
+      <c r="B44">
         <v>20.49</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G42"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G44"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/plantilla_presupuesto.xlsx
+++ b/plantilla_presupuesto.xlsx
@@ -402,10 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A17"/>
-  <cols>
-    <col min="1" max="1" width="110.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:A18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -492,20 +489,21 @@
         <v>Las filas de ejemplo se pueden borrar o sobrescribir.</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>5. En Datos, Valorados y No Valorados: una linea por concepto; salen en los PDF.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A18"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
-  <cols>
-    <col min="1" max="1" width="32.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:B9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -557,15 +555,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>Valorado (una línea por concepto)</v>
+      </c>
+      <c r="B7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>No Valorado (una línea por concepto)</v>
+      </c>
+      <c r="B8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>Descuento carpintero (Sí / No)</v>
       </c>
-      <c r="B7" t="str">
+      <c r="B9" t="str">
         <v>No</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -573,19 +587,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K4"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" customWidth="1"/>
-    <col min="5" max="5" width="22.83203125" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="8.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -737,12 +738,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D2"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -782,12 +777,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D2"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -827,15 +816,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G44"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="34.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
